--- a/templates/request_template.xlsx
+++ b/templates/request_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parrottkim/Projects/javascript/taskflow-backend/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDC4D7B-A27E-114A-AF04-89565F41CCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2586C4-46E8-084F-93EC-C0DCF85A3D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13120" yWindow="520" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="물품구매요청서" sheetId="1" r:id="rId1"/>
@@ -258,46 +258,46 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>금액</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표이사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>울산2공장 ADAS 개조 공사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물품사용용도</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기 판넬 제작 부품 구입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>총액</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>아래 내용 작성 후 부서장 서명 득하고, 해당 직무 담당자(한상일책임)에게 제출-&gt;검토 후
 구매 담당자 지정 외 후속 업무 처리 절차 진행함.
-작성 내용 중 재고 보유에 대해서는 반드시 확인 유무, 수량을 표기 할 것.
+작성 내용 중 재고 보유에 대해서는 반드시 확인 유무, 수량, 필요사항은 비고란에 기입할 것.
 구매 및 지출 결의서 작성, 품의 결재, ERP등록 등 관련사항은 구매 부문에서 진행함</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>금액</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대표이사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로젝트명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>울산2공장 ADAS 개조 공사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>물품사용용도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전기 판넬 제작 부품 구입</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>단가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>총액</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -764,6 +764,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -772,7 +796,58 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -813,81 +888,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1407,18 +1407,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" thickTop="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="26"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2" t="s">
         <v>4</v>
@@ -1427,20 +1427,20 @@
         <v>10</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="24" customHeight="1">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="29"/>
       <c r="K2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1449,48 +1449,48 @@
       <c r="N2" s="6"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="29"/>
       <c r="K3" s="5"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="44"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="29"/>
       <c r="K4" s="5"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="24" customHeight="1">
-      <c r="A5" s="42"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
       <c r="K5" s="5" t="s">
         <v>1</v>
       </c>
@@ -1503,488 +1503,488 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" thickBot="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="32"/>
       <c r="K6" s="10"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
     <row r="7" spans="1:14" ht="83" customHeight="1" thickTop="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="22"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="47"/>
     </row>
     <row r="8" spans="1:14" ht="43.5" customHeight="1">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="23">
+      <c r="B8" s="44"/>
+      <c r="C8" s="48">
         <v>12345678</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="19" t="s">
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="44"/>
+      <c r="J8" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="23" t="s">
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+    </row>
+    <row r="9" spans="1:14" ht="43.5" customHeight="1">
+      <c r="A9" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-    </row>
-    <row r="9" spans="1:14" ht="43.5" customHeight="1">
-      <c r="A9" s="27" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="26"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="51"/>
     </row>
     <row r="10" spans="1:14" ht="43.5" customHeight="1">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="24" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="26"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="51"/>
     </row>
     <row r="11" spans="1:14" ht="62" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="30" t="s">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="32"/>
+      <c r="E11" s="41"/>
       <c r="F11" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="40"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11" s="31"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="30" t="s">
+      <c r="M11" s="40"/>
+      <c r="N11" s="41"/>
+    </row>
+    <row r="12" spans="1:14" ht="40" customHeight="1">
+      <c r="A12" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="15">
+        <v>30</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="23"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="23"/>
+      <c r="N12" s="22"/>
+    </row>
+    <row r="13" spans="1:14" ht="40" customHeight="1">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="22"/>
+    </row>
+    <row r="14" spans="1:14" ht="40" customHeight="1">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="22"/>
+    </row>
+    <row r="15" spans="1:14" ht="40" customHeight="1">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="22"/>
+    </row>
+    <row r="16" spans="1:14" ht="40" customHeight="1">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="22"/>
+    </row>
+    <row r="17" spans="1:14" ht="40" customHeight="1">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="22"/>
+    </row>
+    <row r="18" spans="1:14" ht="40" customHeight="1">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="22"/>
+    </row>
+    <row r="19" spans="1:14" ht="40" customHeight="1">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="22"/>
+    </row>
+    <row r="20" spans="1:14" ht="40" customHeight="1">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="22"/>
+    </row>
+    <row r="21" spans="1:14" ht="40" customHeight="1">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="22"/>
+    </row>
+    <row r="22" spans="1:14" ht="40" customHeight="1">
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="22"/>
+    </row>
+    <row r="23" spans="1:14" ht="40" customHeight="1">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="22"/>
+    </row>
+    <row r="24" spans="1:14" ht="40" customHeight="1">
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="22"/>
+    </row>
+    <row r="25" spans="1:14" ht="40" customHeight="1">
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="22"/>
+    </row>
+    <row r="26" spans="1:14" ht="40" customHeight="1">
+      <c r="A26" s="35"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="22"/>
+    </row>
+    <row r="27" spans="1:14" ht="40" customHeight="1">
+      <c r="A27" s="18"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="22"/>
+    </row>
+    <row r="28" spans="1:14" ht="40" customHeight="1">
+      <c r="A28" s="18"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="22"/>
+    </row>
+    <row r="29" spans="1:14" ht="40" customHeight="1">
+      <c r="A29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="22"/>
+    </row>
+    <row r="30" spans="1:14" ht="40" customHeight="1">
+      <c r="A30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="22"/>
+    </row>
+    <row r="31" spans="1:14" ht="40" customHeight="1">
+      <c r="A31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="22"/>
+    </row>
+    <row r="32" spans="1:14" ht="40" customHeight="1">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="31"/>
-      <c r="N11" s="32"/>
-    </row>
-    <row r="12" spans="1:14" ht="40" customHeight="1">
-      <c r="A12" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="52">
-        <v>30</v>
-      </c>
-      <c r="G12" s="53">
-        <v>0</v>
-      </c>
-      <c r="H12" s="53">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="14"/>
-    </row>
-    <row r="13" spans="1:14" ht="40" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="14"/>
-    </row>
-    <row r="14" spans="1:14" ht="40" customHeight="1">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="14"/>
-    </row>
-    <row r="15" spans="1:14" ht="40" customHeight="1">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="14"/>
-    </row>
-    <row r="16" spans="1:14" ht="40" customHeight="1">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="14"/>
-    </row>
-    <row r="17" spans="1:14" ht="40" customHeight="1">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="14"/>
-    </row>
-    <row r="18" spans="1:14" ht="40" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="14"/>
-    </row>
-    <row r="19" spans="1:14" ht="40" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="14"/>
-    </row>
-    <row r="20" spans="1:14" ht="40" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="14"/>
-    </row>
-    <row r="21" spans="1:14" ht="40" customHeight="1">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="14"/>
-    </row>
-    <row r="22" spans="1:14" ht="40" customHeight="1">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="14"/>
-    </row>
-    <row r="23" spans="1:14" ht="40" customHeight="1">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="14"/>
-    </row>
-    <row r="24" spans="1:14" ht="40" customHeight="1">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="14"/>
-    </row>
-    <row r="25" spans="1:14" ht="40" customHeight="1">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="14"/>
-    </row>
-    <row r="26" spans="1:14" ht="40" customHeight="1">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="14"/>
-    </row>
-    <row r="27" spans="1:14" ht="40" customHeight="1">
-      <c r="A27" s="33"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="14"/>
-    </row>
-    <row r="28" spans="1:14" ht="40" customHeight="1">
-      <c r="A28" s="33"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="14"/>
-    </row>
-    <row r="29" spans="1:14" ht="40" customHeight="1">
-      <c r="A29" s="33"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="14"/>
-    </row>
-    <row r="30" spans="1:14" ht="40" customHeight="1">
-      <c r="A30" s="33"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="14"/>
-    </row>
-    <row r="31" spans="1:14" ht="40" customHeight="1">
-      <c r="A31" s="33"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="14"/>
-    </row>
-    <row r="32" spans="1:14" ht="40" customHeight="1">
-      <c r="A32" s="48"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" s="31"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="50">
+      <c r="J32" s="40"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="33">
         <v>100000000</v>
       </c>
-      <c r="M32" s="50"/>
-      <c r="N32" s="51"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="34" customHeight="1">
       <c r="A33" s="36" t="s">
@@ -2006,25 +2006,56 @@
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="A1:J6"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:N8"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:N9"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="C10:N10"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="A33:N33"/>
     <mergeCell ref="I20:K20"/>
     <mergeCell ref="L20:N20"/>
@@ -2041,69 +2072,38 @@
     <mergeCell ref="I17:K17"/>
     <mergeCell ref="L17:N17"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
     <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="A1:J6"/>
+    <mergeCell ref="D18:E18"/>
     <mergeCell ref="L11:N11"/>
     <mergeCell ref="L12:N12"/>
     <mergeCell ref="L13:N13"/>
     <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L21:N21"/>
     <mergeCell ref="L18:N18"/>
-    <mergeCell ref="I32:K32"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="I29:K29"/>
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="I24:K24"/>
     <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C7:N7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:N8"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:N9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="C10:N10"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D20:E20"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.15" right="0.15" top="0.68" bottom="0.56000000000000005" header="0.5" footer="0.5"/>
